--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,17 +769,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45163.6091171228</v>
+        <v>45232</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>
       <c r="H1" s="17" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
@@ -822,21 +817,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
@@ -868,7 +848,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="20" t="n">
-        <v>125.992</v>
+        <v>200</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
@@ -891,7 +871,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="20" t="n">
-        <v>242.644</v>
+        <v>279.041</v>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
@@ -901,8 +881,6 @@
       <c r="F30" s="21" t="n"/>
       <c r="H30" s="22" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -917,12 +895,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -932,13 +904,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,7 +769,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,7 +769,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45237</v>
+        <v>45244</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>
@@ -904,13 +904,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,7 +769,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>
@@ -904,13 +904,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,7 +769,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,12 +769,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45266</v>
+        <v>45261.57775189915</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>
       <c r="H1" s="17" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
@@ -817,6 +822,21 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
@@ -848,7 +868,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="20" t="n">
-        <v>200</v>
+        <v>221.77</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
@@ -871,7 +891,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="20" t="n">
-        <v>279.041</v>
+        <v>427.11</v>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
@@ -881,6 +901,8 @@
       <c r="F30" s="21" t="n"/>
       <c r="H30" s="22" t="n"/>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -895,6 +917,12 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -904,13 +932,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/RETEN A RODILLO.xlsx
+++ b/LISTAS/ma/RETEN A RODILLO.xlsx
@@ -769,17 +769,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="n">
-        <v>45261.57775189915</v>
+        <v>45286</v>
       </c>
       <c r="F1" s="17" t="n"/>
       <c r="G1" s="17" t="n"/>
       <c r="H1" s="17" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
@@ -822,21 +817,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
@@ -868,7 +848,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="20" t="n">
-        <v>221.77</v>
+        <v>200</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
@@ -891,7 +871,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="20" t="n">
-        <v>427.11</v>
+        <v>279.041</v>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
@@ -901,8 +881,6 @@
       <c r="F30" s="21" t="n"/>
       <c r="H30" s="22" t="n"/>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -917,12 +895,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -932,12 +904,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
